--- a/data/raw/2026-06-21_ST.xlsx
+++ b/data/raw/2026-06-21_ST.xlsx
@@ -5772,7 +5772,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>C L Chau</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5788,11 +5788,7 @@
           <t>8/5/4/11/6/7</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="O92" t="inlineStr"/>
       <c r="P92" t="n">
         <v>20</v>
       </c>
@@ -8066,7 +8062,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>L Hewitson</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8082,11 +8078,7 @@
           <t>7/7/12/2/8/3</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="O131" t="inlineStr"/>
       <c r="P131" t="n">
         <v>20</v>
       </c>
@@ -10405,7 +10397,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>L Hewitson</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -10421,11 +10413,7 @@
           <t>7/7/12/2/8/3</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>20</v>
       </c>
@@ -24644,7 +24632,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>C L Chau</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -24660,11 +24648,7 @@
           <t>8/5/4/11/6/7</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>20</v>
       </c>
